--- a/artfynd/A 50345-2023 artfynd.xlsx
+++ b/artfynd/A 50345-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713723</v>
+        <v>119713730</v>
       </c>
       <c r="B2" t="n">
-        <v>56514</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466882</v>
+        <v>466837</v>
       </c>
       <c r="R2" t="n">
-        <v>7074791</v>
+        <v>7074776</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>hörd</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713730</v>
+        <v>119713723</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +798,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466837</v>
+        <v>466882</v>
       </c>
       <c r="R3" t="n">
-        <v>7074776</v>
+        <v>7074791</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>hörd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713729</v>
+        <v>119713718</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466892</v>
+        <v>466840</v>
       </c>
       <c r="R5" t="n">
-        <v>7074824</v>
+        <v>7074771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713718</v>
+        <v>119713729</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466840</v>
+        <v>466892</v>
       </c>
       <c r="R6" t="n">
-        <v>7074771</v>
+        <v>7074824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50345-2023 artfynd.xlsx
+++ b/artfynd/A 50345-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713723</v>
+        <v>119713719</v>
       </c>
       <c r="B3" t="n">
-        <v>56514</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -816,20 +816,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466882</v>
+        <v>466835</v>
       </c>
       <c r="R3" t="n">
-        <v>7074791</v>
+        <v>7074749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>hörd</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713719</v>
+        <v>119713729</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466835</v>
+        <v>466892</v>
       </c>
       <c r="R4" t="n">
-        <v>7074749</v>
+        <v>7074824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1107,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713729</v>
+        <v>119713723</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>56514</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,34 +1119,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466892</v>
+        <v>466882</v>
       </c>
       <c r="R6" t="n">
-        <v>7074824</v>
+        <v>7074791</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>hörd</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50345-2023 artfynd.xlsx
+++ b/artfynd/A 50345-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713719</v>
+        <v>119713729</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466835</v>
+        <v>466892</v>
       </c>
       <c r="R3" t="n">
-        <v>7074749</v>
+        <v>7074824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713729</v>
+        <v>119713718</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466892</v>
+        <v>466840</v>
       </c>
       <c r="R4" t="n">
-        <v>7074824</v>
+        <v>7074771</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713718</v>
+        <v>119713723</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>56514</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1030,16 +1030,20 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466840</v>
+        <v>466882</v>
       </c>
       <c r="R5" t="n">
-        <v>7074771</v>
+        <v>7074791</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>hörd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713723</v>
+        <v>119713719</v>
       </c>
       <c r="B6" t="n">
-        <v>56514</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,16 +1123,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1137,20 +1141,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466882</v>
+        <v>466835</v>
       </c>
       <c r="R6" t="n">
-        <v>7074791</v>
+        <v>7074749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hörd</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50345-2023 artfynd.xlsx
+++ b/artfynd/A 50345-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713730</v>
+        <v>119713723</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>56524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466837</v>
+        <v>466882</v>
       </c>
       <c r="R2" t="n">
-        <v>7074776</v>
+        <v>7074791</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>hörd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713729</v>
+        <v>119713719</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466892</v>
+        <v>466835</v>
       </c>
       <c r="R3" t="n">
-        <v>7074824</v>
+        <v>7074749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713718</v>
+        <v>119713729</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466840</v>
+        <v>466892</v>
       </c>
       <c r="R4" t="n">
-        <v>7074771</v>
+        <v>7074824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713723</v>
+        <v>119713730</v>
       </c>
       <c r="B5" t="n">
-        <v>56514</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,38 +1016,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466882</v>
+        <v>466837</v>
       </c>
       <c r="R5" t="n">
-        <v>7074791</v>
+        <v>7074776</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>hörd</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713719</v>
+        <v>119713718</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466835</v>
+        <v>466840</v>
       </c>
       <c r="R6" t="n">
-        <v>7074749</v>
+        <v>7074771</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50345-2023 artfynd.xlsx
+++ b/artfynd/A 50345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119713723</v>
+        <v>119713729</v>
       </c>
       <c r="B2" t="n">
-        <v>56524</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>sandberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466882</v>
+        <v>466892</v>
       </c>
       <c r="R2" t="n">
-        <v>7074791</v>
+        <v>7074824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>hörd</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119713719</v>
+        <v>119713730</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466835</v>
+        <v>466837</v>
       </c>
       <c r="R3" t="n">
-        <v>7074749</v>
+        <v>7074776</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713729</v>
+        <v>119713720</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>466892</v>
+        <v>466855</v>
       </c>
       <c r="R4" t="n">
-        <v>7074824</v>
+        <v>7074705</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713730</v>
+        <v>119713718</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466837</v>
+        <v>466840</v>
       </c>
       <c r="R5" t="n">
-        <v>7074776</v>
+        <v>7074771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1051,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,15 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713718</v>
+        <v>119713719</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>466840</v>
+        <v>466835</v>
       </c>
       <c r="R6" t="n">
-        <v>7074771</v>
+        <v>7074749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1153,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,6 +1177,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119713723</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>sandberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>466882</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7074791</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hörd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50345-2023 artfynd.xlsx
+++ b/artfynd/A 50345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713729</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713730</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713720</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713718</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713719</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,8 +1313,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713723</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>